--- a/ConfigSource/库存系统/库存系统数值表.xlsx
+++ b/ConfigSource/库存系统/库存系统数值表.xlsx
@@ -2,15 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R00613649415f4356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品组" sheetId="2" r:id="R262c93d7a0464225"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品" sheetId="3" r:id="R60748ab26b3f4922"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位表现" sheetId="4" r:id="Rb712ef86573e45b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建筑槽位规则" sheetId="5" r:id="Rd10ee2703b9d4680"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仓储分类修正" sheetId="6" r:id="R8a0ad0b8c16949d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="居民饮食" sheetId="7" r:id="R89877e5f81cd436d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位类型" sheetId="8" r:id="Ra1ca5a7867004642"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位分类修正" sheetId="9" r:id="Rb1a89948ad884d62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R5d14937a9eda4bfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品组" sheetId="2" r:id="R680084420faa4350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品" sheetId="3" r:id="R1ffe20424d48427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位类型" sheetId="8" r:id="R56d25894e68249a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位分类修正" sheetId="9" r:id="R1abaf4731e7346c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -600,55 +596,6 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="InventorySlotPresentationsTable" displayName="InventorySlotPresentationsTable" ref="A4:H9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H9"/>
-  <x:tableColumns count="8">
-    <x:tableColumn id="1" name="PresentationId"/>
-    <x:tableColumn id="2" name="名称"/>
-    <x:tableColumn id="3" name="SlotViewPrefabPath"/>
-    <x:tableColumn id="4" name="BackgroundSpritePath"/>
-    <x:tableColumn id="5" name="OverlaySpritePath"/>
-    <x:tableColumn id="6" name="BackgroundTint"/>
-    <x:tableColumn id="7" name="ContentTint"/>
-    <x:tableColumn id="8" name="OverlayTint"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="InventoryBuildingSlotRulesTable" displayName="InventoryBuildingSlotRulesTable" ref="A4:G11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:G11"/>
-  <x:tableColumns count="7">
-    <x:tableColumn id="1" name="FamilyId"/>
-    <x:tableColumn id="2" name="Level"/>
-    <x:tableColumn id="3" name="建筑表格数(只读校验)"/>
-    <x:tableColumn id="4" name="基础损耗倍率"/>
-    <x:tableColumn id="5" name="槽位主题"/>
-    <x:tableColumn id="6" name="PresentationId"/>
-    <x:tableColumn id="7" name="自动存放优先级"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="InventoryResidentialDietTable" displayName="InventoryResidentialDietTable" ref="A4:G8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:G8"/>
-  <x:tableColumns count="7">
-    <x:tableColumn id="1" name="FamilyId"/>
-    <x:tableColumn id="2" name="Level"/>
-    <x:tableColumn id="3" name="FoodGroupId"/>
-    <x:tableColumn id="4" name="选择策略"/>
-    <x:tableColumn id="5" name="目标饮食种类"/>
-    <x:tableColumn id="6" name="生活质量变化/回合"/>
-    <x:tableColumn id="7" name="高质量增长阈值"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -890,16 +837,17 @@
         <x:v>SchemaVersion</x:v>
       </x:c>
       <x:c r="B4" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D4" s="52" t="str">
         <x:v>1. 表头固定在第 4 行，数据从第 5 行开始。
 2. 物品和物品组使用稳定 ID；多值用分号分隔。
-3. 物品每回合损耗率按 0~1 填写。
-4. 实际逐格损耗 = floor(数量 × 物品基础损耗率 × 槽位类型基础倍率 × 分类倍率 × 建筑运行时倍率)。
-5. 槽位类型表不允许出现 FamilyId 或 Level。
-6. 槽位视觉不从 Excel 导入，由 UI 代码按 InventorySlotType 处理。
-7. Unity 菜单：Landsong/Inventory/库存数值导表工具。</x:v>
+3. 物品每回合损耗率按 0～1 填写。
+4. 自动入库统一选择该物品有效损耗率最低的可用槽位；同损耗率优先合并已有堆叠。
+5. 有效损耗率 = 物品基础损耗率 × 槽位类型基础倍率 × 分类倍率 × 建筑运行时倍率。
+6. 建筑提供的槽位类型和数量由建筑数值表管理。
+7. 槽位视觉不从 Excel 导入，由 UI 代码按 InventorySlotType 处理。
+8. Unity 菜单：Landsong/Inventory/库存数值导表工具。</x:v>
       </x:c>
       <x:c r="E4" s="53"/>
       <x:c r="F4" s="54"/>
@@ -947,7 +895,8 @@
         <x:v>槽位类型</x:v>
       </x:c>
       <x:c r="B9" s="31" t="n">
-        <x:v>12</x:v>
+        <x:f>COUNTA('槽位类型'!A5:A204)</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="55"/>
       <x:c r="E9" s="56"/>
@@ -958,7 +907,8 @@
         <x:v>槽位分类修正</x:v>
       </x:c>
       <x:c r="B10" s="31" t="n">
-        <x:v>1</x:v>
+        <x:f>COUNTA('槽位分类修正'!A5:A204)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="55"/>
       <x:c r="E10" s="56"/>
@@ -1070,7 +1020,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08e41d9aa9fc42f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56332bd8ebea4756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1749,722 +1699,12 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d7a6c0228e8479d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64d3ca9113714835"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="44" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="44" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="62" t="str">
-        <x:v>已停用：槽位表现不再由数值表管理</x:v>
-      </x:c>
-      <x:c r="B1" s="62"/>
-      <x:c r="C1" s="62"/>
-      <x:c r="D1" s="62"/>
-      <x:c r="E1" s="62"/>
-      <x:c r="F1" s="62"/>
-      <x:c r="G1" s="62"/>
-      <x:c r="H1" s="62"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="12" t="str">
-        <x:v>槽位视觉由 UI 代码按 InventorySlotType 解析。本页不参与导入。</x:v>
-      </x:c>
-      <x:c r="B2" s="13"/>
-      <x:c r="C2" s="13"/>
-      <x:c r="D2" s="13"/>
-      <x:c r="E2" s="13"/>
-      <x:c r="F2" s="13"/>
-      <x:c r="G2" s="13"/>
-      <x:c r="H2" s="14"/>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="70"/>
-      <x:c r="B4" s="71"/>
-      <x:c r="C4" s="71"/>
-      <x:c r="D4" s="71"/>
-      <x:c r="E4" s="71"/>
-      <x:c r="F4" s="71"/>
-      <x:c r="G4" s="71"/>
-      <x:c r="H4" s="72"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="83"/>
-      <x:c r="B5" s="83"/>
-      <x:c r="C5" s="83"/>
-      <x:c r="D5" s="83"/>
-      <x:c r="E5" s="83"/>
-      <x:c r="F5" s="83"/>
-      <x:c r="G5" s="83"/>
-      <x:c r="H5" s="83"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="84"/>
-      <x:c r="B6" s="84"/>
-      <x:c r="C6" s="84"/>
-      <x:c r="D6" s="84"/>
-      <x:c r="E6" s="84"/>
-      <x:c r="F6" s="84"/>
-      <x:c r="G6" s="84"/>
-      <x:c r="H6" s="84"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="84"/>
-      <x:c r="B7" s="84"/>
-      <x:c r="C7" s="84"/>
-      <x:c r="D7" s="84"/>
-      <x:c r="E7" s="84"/>
-      <x:c r="F7" s="84"/>
-      <x:c r="G7" s="84"/>
-      <x:c r="H7" s="84"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="84"/>
-      <x:c r="B8" s="84"/>
-      <x:c r="C8" s="84"/>
-      <x:c r="D8" s="84"/>
-      <x:c r="E8" s="84"/>
-      <x:c r="F8" s="84"/>
-      <x:c r="G8" s="84"/>
-      <x:c r="H8" s="84"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="85"/>
-      <x:c r="B9" s="85"/>
-      <x:c r="C9" s="85"/>
-      <x:c r="D9" s="85"/>
-      <x:c r="E9" s="85"/>
-      <x:c r="F9" s="85"/>
-      <x:c r="G9" s="85"/>
-      <x:c r="H9" s="85"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cf708f02aa445d6"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="62" t="str">
-        <x:v>已移除：库存表不再读取建筑等级</x:v>
-      </x:c>
-      <x:c r="B1" s="62"/>
-      <x:c r="C1" s="62"/>
-      <x:c r="D1" s="62"/>
-      <x:c r="E1" s="62"/>
-      <x:c r="F1" s="62"/>
-      <x:c r="G1" s="62"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="12" t="str">
-        <x:v>建筑提供哪种槽位及数量由建筑数值表负责。本页不参与导入。</x:v>
-      </x:c>
-      <x:c r="B2" s="13"/>
-      <x:c r="C2" s="13"/>
-      <x:c r="D2" s="13"/>
-      <x:c r="E2" s="13"/>
-      <x:c r="F2" s="13"/>
-      <x:c r="G2" s="14"/>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="70"/>
-      <x:c r="B4" s="71"/>
-      <x:c r="C4" s="71"/>
-      <x:c r="D4" s="71"/>
-      <x:c r="E4" s="71"/>
-      <x:c r="F4" s="71"/>
-      <x:c r="G4" s="72"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="83"/>
-      <x:c r="B5" s="83"/>
-      <x:c r="C5" s="83"/>
-      <x:c r="D5" s="90"/>
-      <x:c r="E5" s="83"/>
-      <x:c r="F5" s="83"/>
-      <x:c r="G5" s="83"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="84"/>
-      <x:c r="B6" s="84"/>
-      <x:c r="C6" s="84"/>
-      <x:c r="D6" s="91"/>
-      <x:c r="E6" s="84"/>
-      <x:c r="F6" s="84"/>
-      <x:c r="G6" s="84"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="84"/>
-      <x:c r="B7" s="84"/>
-      <x:c r="C7" s="84"/>
-      <x:c r="D7" s="91"/>
-      <x:c r="E7" s="84"/>
-      <x:c r="F7" s="84"/>
-      <x:c r="G7" s="84"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="84"/>
-      <x:c r="B8" s="84"/>
-      <x:c r="C8" s="84"/>
-      <x:c r="D8" s="91"/>
-      <x:c r="E8" s="84"/>
-      <x:c r="F8" s="84"/>
-      <x:c r="G8" s="84"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="84"/>
-      <x:c r="B9" s="84"/>
-      <x:c r="C9" s="84"/>
-      <x:c r="D9" s="91"/>
-      <x:c r="E9" s="84"/>
-      <x:c r="F9" s="84"/>
-      <x:c r="G9" s="84"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="84"/>
-      <x:c r="B10" s="84"/>
-      <x:c r="C10" s="84"/>
-      <x:c r="D10" s="91"/>
-      <x:c r="E10" s="84"/>
-      <x:c r="F10" s="84"/>
-      <x:c r="G10" s="84"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="85"/>
-      <x:c r="B11" s="85"/>
-      <x:c r="C11" s="85"/>
-      <x:c r="D11" s="92"/>
-      <x:c r="E11" s="85"/>
-      <x:c r="F11" s="85"/>
-      <x:c r="G11" s="85"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="D12" s="93"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="D13" s="93"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="D14" s="93"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="D15" s="93"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="D16" s="93"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="D17" s="93"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="D18" s="93"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="D19" s="93"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="D20" s="93"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="D21" s="93"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="D22" s="93"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="D23" s="93"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="D24" s="93"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="D25" s="93"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="D26" s="93"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="D27" s="93"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="D28" s="93"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="D29" s="93"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="D30" s="93"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="D31" s="93"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="D32" s="93"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="D33" s="93"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="D34" s="93"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="D35" s="93"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="D36" s="93"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="D37" s="93"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="D38" s="93"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="D39" s="93"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="D40" s="93"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
-  </x:mergeCells>
-  <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="E5:E40">
-      <x:formula1>"Default,Palace,BasicWarehouse,Warehouse,AdvancedWarehouse,ColdStorage,Cellar,Granary,Armory"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="D5:D40">
-      <x:formula1>0</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ba79451dd0b49f4"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="62" t="str">
-        <x:v>已迁移：请使用“槽位分类修正”</x:v>
-      </x:c>
-      <x:c r="B1" s="62"/>
-      <x:c r="C1" s="62"/>
-      <x:c r="D1" s="62"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="12" t="str">
-        <x:v>修正规则现在按 SlotType + ItemGroupId 配置，不再使用 FamilyId + Level。</x:v>
-      </x:c>
-      <x:c r="B2" s="13"/>
-      <x:c r="C2" s="13"/>
-      <x:c r="D2" s="14"/>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="70"/>
-      <x:c r="B4" s="71"/>
-      <x:c r="C4" s="71"/>
-      <x:c r="D4" s="72"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="D5" s="93"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="D6" s="93"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="D7" s="93"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="D8" s="93"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="D9" s="93"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="D10" s="93"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="D11" s="93"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="D12" s="93"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="D13" s="93"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="D14" s="93"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="D15" s="93"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="D16" s="93"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="D17" s="93"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="D18" s="93"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="D19" s="93"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="D20" s="93"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="D21" s="93"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="D22" s="93"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="D23" s="93"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="D24" s="93"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="D25" s="93"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="D26" s="93"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="D27" s="93"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="D28" s="93"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="D29" s="93"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="D30" s="93"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="D31" s="93"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="D32" s="93"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="D33" s="93"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="D34" s="93"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="D35" s="93"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="D36" s="93"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="D37" s="93"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="D38" s="93"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="D39" s="93"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="D40" s="93"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
-  </x:mergeCells>
-  <x:dataValidations count="1">
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="D5:D40">
-      <x:formula1>0</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="62" t="str">
-        <x:v>已迁移：居民饮食属于建筑配置</x:v>
-      </x:c>
-      <x:c r="B1" s="62"/>
-      <x:c r="C1" s="62"/>
-      <x:c r="D1" s="62"/>
-      <x:c r="E1" s="62"/>
-      <x:c r="F1" s="62"/>
-      <x:c r="G1" s="62"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="12" t="str">
-        <x:v>正式配置已经迁入建筑数值表的“等级_住宅”。本页不参与库存导入。</x:v>
-      </x:c>
-      <x:c r="B2" s="13"/>
-      <x:c r="C2" s="13"/>
-      <x:c r="D2" s="13"/>
-      <x:c r="E2" s="13"/>
-      <x:c r="F2" s="13"/>
-      <x:c r="G2" s="14"/>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="70"/>
-      <x:c r="B4" s="71"/>
-      <x:c r="C4" s="71"/>
-      <x:c r="D4" s="71"/>
-      <x:c r="E4" s="71"/>
-      <x:c r="F4" s="71"/>
-      <x:c r="G4" s="72"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="83"/>
-      <x:c r="B5" s="83"/>
-      <x:c r="C5" s="83"/>
-      <x:c r="D5" s="83"/>
-      <x:c r="E5" s="83"/>
-      <x:c r="F5" s="90"/>
-      <x:c r="G5" s="90"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="84"/>
-      <x:c r="B6" s="84"/>
-      <x:c r="C6" s="84"/>
-      <x:c r="D6" s="84"/>
-      <x:c r="E6" s="84"/>
-      <x:c r="F6" s="91"/>
-      <x:c r="G6" s="91"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="84"/>
-      <x:c r="B7" s="84"/>
-      <x:c r="C7" s="84"/>
-      <x:c r="D7" s="84"/>
-      <x:c r="E7" s="84"/>
-      <x:c r="F7" s="91"/>
-      <x:c r="G7" s="91"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="85"/>
-      <x:c r="B8" s="85"/>
-      <x:c r="C8" s="85"/>
-      <x:c r="D8" s="85"/>
-      <x:c r="E8" s="85"/>
-      <x:c r="F8" s="92"/>
-      <x:c r="G8" s="92"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="F9" s="93"/>
-      <x:c r="G9" s="93"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="F10" s="93"/>
-      <x:c r="G10" s="93"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="F11" s="93"/>
-      <x:c r="G11" s="93"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="F12" s="93"/>
-      <x:c r="G12" s="93"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="F13" s="93"/>
-      <x:c r="G13" s="93"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="F14" s="93"/>
-      <x:c r="G14" s="93"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="F15" s="93"/>
-      <x:c r="G15" s="93"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="F16" s="93"/>
-      <x:c r="G16" s="93"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="F17" s="93"/>
-      <x:c r="G17" s="93"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="F18" s="93"/>
-      <x:c r="G18" s="93"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="F19" s="93"/>
-      <x:c r="G19" s="93"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="F20" s="93"/>
-      <x:c r="G20" s="93"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="F21" s="93"/>
-      <x:c r="G21" s="93"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="F22" s="93"/>
-      <x:c r="G22" s="93"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="F23" s="93"/>
-      <x:c r="G23" s="93"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="F24" s="93"/>
-      <x:c r="G24" s="93"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="F25" s="93"/>
-      <x:c r="G25" s="93"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="F26" s="93"/>
-      <x:c r="G26" s="93"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="F27" s="93"/>
-      <x:c r="G27" s="93"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="F28" s="93"/>
-      <x:c r="G28" s="93"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="F29" s="93"/>
-      <x:c r="G29" s="93"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="F30" s="93"/>
-      <x:c r="G30" s="93"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="F31" s="93"/>
-      <x:c r="G31" s="93"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="F32" s="93"/>
-      <x:c r="G32" s="93"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="F33" s="93"/>
-      <x:c r="G33" s="93"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="F34" s="93"/>
-      <x:c r="G34" s="93"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="F35" s="93"/>
-      <x:c r="G35" s="93"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="F36" s="93"/>
-      <x:c r="G36" s="93"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="F37" s="93"/>
-      <x:c r="G37" s="93"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="F38" s="93"/>
-      <x:c r="G38" s="93"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="F39" s="93"/>
-      <x:c r="G39" s="93"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="F40" s="93"/>
-      <x:c r="G40" s="93"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
-  </x:mergeCells>
-  <x:dataValidations count="3">
-    <x:dataValidation type="list" sqref="D5:D40">
-      <x:formula1>"PreferSoonToSpoil,PreferVariety,PreferQuality,PreferLowestValue"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="F5:F40">
-      <x:formula1>0</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="G5:G40">
-      <x:formula1>0</x:formula1>
-      <x:formula2>100</x:formula2>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R973145893b994beb"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2480,15 +1720,15 @@
       </x:c>
       <x:c r="B1" s="100"/>
       <x:c r="C1" s="100"/>
-      <x:c r="D1" s="100"/>
+      <x:c r="D1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="104" t="str">
-        <x:v>SlotType 是建筑系统与库存系统的稳定契约。建筑只提供类型和数量；本表统一管理基础损耗倍率与自动存放优先级，视觉由代码控制。</x:v>
+        <x:v>SlotType 是建筑系统与库存系统的稳定契约。建筑只提供类型和数量；本表统一管理基础损耗倍率。自动入库始终选择该物品有效损耗率最低的可用槽位。</x:v>
       </x:c>
       <x:c r="B2" s="104"/>
       <x:c r="C2" s="104"/>
-      <x:c r="D2" s="104"/>
+      <x:c r="D2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="109" t="str">
@@ -2500,177 +1740,109 @@
       <x:c r="C4" s="109" t="str">
         <x:v>基础损耗倍率</x:v>
       </x:c>
-      <x:c r="D4" s="109" t="str">
-        <x:v>自动存放优先级</x:v>
-      </x:c>
+      <x:c r="D4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="110" t="str">
-        <x:v>Default</x:v>
+        <x:v>简陋库存</x:v>
       </x:c>
       <x:c r="B5" s="110" t="str">
-        <x:v>普通格</x:v>
+        <x:v>简陋库存</x:v>
       </x:c>
       <x:c r="C5" s="111" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="110" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="97" t="str">
-        <x:v>Palace</x:v>
+        <x:v>普通库存</x:v>
       </x:c>
       <x:c r="B6" s="97" t="str">
-        <x:v>王宫格Ⅰ</x:v>
+        <x:v>普通库存</x:v>
       </x:c>
       <x:c r="C6" s="112" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="97" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="D6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="110" t="str">
-        <x:v>PalaceImproved</x:v>
+        <x:v>高级库存</x:v>
       </x:c>
       <x:c r="B7" s="110" t="str">
-        <x:v>王宫格Ⅱ</x:v>
+        <x:v>高级库存</x:v>
       </x:c>
       <x:c r="C7" s="111" t="n">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="D7" s="110" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="D7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="97" t="str">
-        <x:v>PalaceAdvanced</x:v>
+        <x:v>冻库</x:v>
       </x:c>
       <x:c r="B8" s="97" t="str">
-        <x:v>王宫格Ⅲ</x:v>
+        <x:v>冻库</x:v>
       </x:c>
       <x:c r="C8" s="112" t="n">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="D8" s="97" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="110" t="str">
-        <x:v>PalaceRoyal</x:v>
+        <x:v>粮库</x:v>
       </x:c>
       <x:c r="B9" s="110" t="str">
-        <x:v>王宫格Ⅳ</x:v>
+        <x:v>粮库</x:v>
       </x:c>
       <x:c r="C9" s="111" t="n">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="D9" s="110" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="97" t="str">
-        <x:v>BasicWarehouse</x:v>
-      </x:c>
-      <x:c r="B10" s="97" t="str">
-        <x:v>低级仓库格</x:v>
-      </x:c>
-      <x:c r="C10" s="112" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="97" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="A10" s="97"/>
+      <x:c r="B10" s="97"/>
+      <x:c r="C10" s="112"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="110" t="str">
-        <x:v>Warehouse</x:v>
-      </x:c>
-      <x:c r="B11" s="110" t="str">
-        <x:v>标准仓库格</x:v>
-      </x:c>
-      <x:c r="C11" s="111" t="n">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="D11" s="110" t="n">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="A11" s="110"/>
+      <x:c r="B11" s="110"/>
+      <x:c r="C11" s="111"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="97" t="str">
-        <x:v>AdvancedWarehouse</x:v>
-      </x:c>
-      <x:c r="B12" s="97" t="str">
-        <x:v>高级仓库格</x:v>
-      </x:c>
-      <x:c r="C12" s="112" t="n">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="D12" s="97" t="n">
-        <x:v>30</x:v>
-      </x:c>
+      <x:c r="A12" s="97"/>
+      <x:c r="B12" s="97"/>
+      <x:c r="C12" s="112"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="110" t="str">
-        <x:v>ColdStorage</x:v>
-      </x:c>
-      <x:c r="B13" s="110" t="str">
-        <x:v>冻库格</x:v>
-      </x:c>
-      <x:c r="C13" s="111" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="110" t="n">
-        <x:v>40</x:v>
-      </x:c>
+      <x:c r="A13" s="110"/>
+      <x:c r="B13" s="110"/>
+      <x:c r="C13" s="111"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="97" t="str">
-        <x:v>Cellar</x:v>
-      </x:c>
-      <x:c r="B14" s="97" t="str">
-        <x:v>地窖格</x:v>
-      </x:c>
-      <x:c r="C14" s="112" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="97" t="n">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="A14" s="97"/>
+      <x:c r="B14" s="97"/>
+      <x:c r="C14" s="112"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="110" t="str">
-        <x:v>Granary</x:v>
-      </x:c>
-      <x:c r="B15" s="110" t="str">
-        <x:v>粮仓格</x:v>
-      </x:c>
-      <x:c r="C15" s="111" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="110" t="n">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="A15" s="110"/>
+      <x:c r="B15" s="110"/>
+      <x:c r="C15" s="111"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="97" t="str">
-        <x:v>Armory</x:v>
-      </x:c>
-      <x:c r="B16" s="97" t="str">
-        <x:v>军械库格</x:v>
-      </x:c>
-      <x:c r="C16" s="112" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="97" t="n">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="A16" s="97"/>
+      <x:c r="B16" s="97"/>
+      <x:c r="C16" s="112"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="C17" s="93"/>
@@ -2746,19 +1918,22 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A2:C2"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="A5:A40">
       <x:formula1>"Default,Palace,PalaceImproved,PalaceAdvanced,PalaceRoyal,BasicWarehouse,Warehouse,AdvancedWarehouse,ColdStorage,Cellar,Granary,Armory"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="A5:A204">
+      <x:formula1>"简陋库存,普通库存,高级库存,冻库,粮库"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2794,7 +1969,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="110" t="str">
-        <x:v>ColdStorage</x:v>
+        <x:v>冻库</x:v>
       </x:c>
       <x:c r="B5" s="110" t="str">
         <x:v>food</x:v>
@@ -2804,7 +1979,15 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="C6" s="93"/>
+      <x:c r="A6" t="str">
+        <x:v>粮库</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>food</x:v>
+      </x:c>
+      <x:c r="C6" s="93" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="C7" s="93"/>
@@ -2913,9 +2096,12 @@
     <x:mergeCell ref="A1:C1"/>
     <x:mergeCell ref="A2:C2"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="A5:A40">
       <x:formula1>"Default,Palace,PalaceImproved,PalaceAdvanced,PalaceRoyal,BasicWarehouse,Warehouse,AdvancedWarehouse,ColdStorage,Cellar,Granary,Armory"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="A5:A204">
+      <x:formula1>"简陋库存,普通库存,高级库存,冻库,粮库"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ConfigSource/库存系统/库存系统数值表.xlsx
+++ b/ConfigSource/库存系统/库存系统数值表.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R5d14937a9eda4bfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品组" sheetId="2" r:id="R680084420faa4350"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品" sheetId="3" r:id="R1ffe20424d48427e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位类型" sheetId="8" r:id="R56d25894e68249a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位分类修正" sheetId="9" r:id="R1abaf4731e7346c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R0ebb4a44714d46bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品组" sheetId="2" r:id="Re3ec98969a3646b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品" sheetId="3" r:id="R9084cca53af546bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位类型" sheetId="8" r:id="R44eae4c3b3e241d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槽位分类修正" sheetId="9" r:id="R332a3444daee4adc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -559,8 +559,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryItemGroupsTable" displayName="InventoryItemGroupsTable" ref="A4:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:E5"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryItemGroupsTable" displayName="InventoryItemGroupsTable" ref="A4:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:E7"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="GroupId"/>
     <x:tableColumn id="2" name="名称"/>
@@ -573,8 +573,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="InventoryItemsTable" displayName="InventoryItemsTable" ref="A4:O15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:O15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="InventoryItemsTable" displayName="InventoryItemsTable" ref="A4:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:O16"/>
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="ItemId"/>
     <x:tableColumn id="2" name="名称"/>
@@ -873,7 +873,8 @@
         <x:v>物品组</x:v>
       </x:c>
       <x:c r="B7" s="30" t="n">
-        <x:v>2</x:v>
+        <x:f>COUNTA('物品组'!A5:A204)</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="55"/>
       <x:c r="E7" s="56"/>
@@ -884,7 +885,8 @@
         <x:v>物品</x:v>
       </x:c>
       <x:c r="B8" s="31" t="n">
-        <x:v>11</x:v>
+        <x:f>COUNTA('物品'!A5:A204)</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="55"/>
       <x:c r="E8" s="56"/>
@@ -1013,6 +1015,21 @@
       </x:c>
       <x:c r="E6" s="97"/>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>food.grain</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>谷物</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>小麦等谷物物品，可作为稳定的主食来源。</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>food</x:v>
+      </x:c>
+      <x:c r="E7"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
@@ -1020,7 +1037,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56332bd8ebea4756"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45539058694d4c48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1549,9 +1566,45 @@
       <x:c r="O15" s="85" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="J16" s="89"/>
-      <x:c r="M16" s="93"/>
-      <x:c r="N16" s="93"/>
+      <x:c r="A16" t="str">
+        <x:v>小麦</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>小麦</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>可作为谷物满足居民的主食需求。</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Food</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F16" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16" s="89" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>food.grain</x:v>
+      </x:c>
+      <x:c r="L16" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M16" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N16" s="93" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O16"/>
     </x:row>
     <x:row r="17">
       <x:c r="J17" s="89"/>
@@ -1699,7 +1752,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64d3ca9113714835"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4091d4d9ce1544f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
